--- a/main/ig/StructureDefinition-fr-lm-service-request.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-service-request.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-service-request.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-service-request.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-service-request.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-service-request.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-service-request.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-service-request.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-service-request.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="171">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -491,6 +491,9 @@
   </si>
   <si>
     <t>Priorité de la demande</t>
+  </si>
+  <si>
+    <t>preferred</t>
   </si>
   <si>
     <t>(preferred): HL7 Request Priority</t>
@@ -3256,10 +3259,10 @@
         <v>73</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>73</v>
@@ -3297,10 +3300,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3323,13 +3326,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3380,7 +3383,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3397,10 +3400,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3423,13 +3426,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3480,7 +3483,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3497,10 +3500,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3523,13 +3526,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3580,7 +3583,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3597,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3623,13 +3626,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3680,7 +3683,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -3697,10 +3700,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3723,13 +3726,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3780,7 +3783,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
